--- a/astro-site/public/dl/kit-tareas-chocolateria/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/BONUS-01-briefing-servicio.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Briefing'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +81,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -143,54 +150,65 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -550,15 +568,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -566,6 +585,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -594,9 +614,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -618,8 +636,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -628,18 +663,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -656,6 +691,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -795,6 +831,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -915,6 +952,7 @@
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="13" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -1035,6 +1073,7 @@
       <c r="F24" s="11" t="n"/>
       <c r="G24" s="13" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
@@ -1154,6 +1193,26 @@
       <c r="E31" s="12" t="n"/>
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="13" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C32">
+        <f>COUNTIF(E6:E31,"✓")</f>
+        <v>3.0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E32">
+        <f>COUNTIF(B6:B31,"?*")</f>
+        <v>20.0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -1180,11 +1239,25 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G31">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E21 E22 E23 E24 E28 E29 E30 E31" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E21 E22 E23 E24 E28 E29 E30 E31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-chocolateria/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/BONUS-01-briefing-servicio.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -640,7 +640,14 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -665,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -831,77 +838,77 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Temperatura y humedad del obrador al arrancar: ____ °C / ____ % (objetivo 18-20 °C y menos del 60 %)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="13" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Pedidos especiales</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Pedido 1: _____________ — Entrega: ___/___</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Pedido 2: _____________ — Entrega: ___/___</t>
+          <t>Pedido 1: _____________ — Entrega: ___/___</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -916,11 +923,11 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Pedido 3: _____________ — Entrega: ___/___</t>
+          <t>Pedido 2: _____________ — Entrega: ___/___</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -935,11 +942,11 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Pedidos online pendientes: ___________________________</t>
+          <t>Pedido 3: _____________ — Entrega: ___/___</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -952,77 +959,77 @@
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="13" t="n"/>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Pedidos online pendientes: ___________________________</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Equipo del turno</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Obrador: ___________________________</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Tienda: ___________________________</t>
+          <t>Obrador: ___________________________</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -1037,11 +1044,11 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Encargado: ___________________________</t>
+          <t>Tienda: ___________________________</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -1056,11 +1063,11 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Ausencias / cambios: ___________________________</t>
+          <t>Encargado: ___________________________</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -1073,82 +1080,82 @@
       <c r="F24" s="11" t="n"/>
       <c r="G24" s="13" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Ausencias / cambios: ___________________________</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="13" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Notas y promociones</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Producto destacado del día: ___________________________</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Tienda</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Promoción activa: ___________________________</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>RRSS</t>
+          <t>Producto destacado del día: ___________________________</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="D29" s="11" t="n"/>
@@ -1158,16 +1165,16 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Eventos / visitas especiales: ___________________________</t>
+          <t>Promoción activa: ___________________________</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>RRSS</t>
         </is>
       </c>
       <c r="D30" s="11" t="n"/>
@@ -1177,11 +1184,11 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Incidencias del turno anterior: ___________________________</t>
+          <t>Eventos / visitas especiales: ___________________________</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -1195,58 +1202,77 @@
       <c r="G31" s="13" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="18" t="inlineStr">
+      <c r="A32" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Incidencias del turno anterior: ___________________________</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C32">
-        <f>COUNTIF(E6:E31,"✓")</f>
-        <v>3.0</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33">
+        <f>COUNTIFS(B6:B32,"?*",E6:E32,"✓")-COUNTIFS(B6:B32,"Tarea",E6:E32,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E32">
-        <f>COUNTIF(B6:B31,"?*")</f>
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E33">
+        <f>COUNTIF(B6:B32,"?*")-COUNTIF(B6:B32,"Tarea")-COUNTIF(E6:E32,"N/A")</f>
+        <v>18.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A13:G13"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G31">
+  <conditionalFormatting sqref="A6:G32">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E21 E22 E23 E24 E28 E29 E30 E31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E22 E23 E24 E25 E29 E30 E31 E32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-chocolateria/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/BONUS-01-briefing-servicio.xlsx
@@ -1257,8 +1257,8 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A34:G34"/>
